--- a/output/yearly_total_coral_cover_iteration_27_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_27_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.248995564577958</v>
+        <v>1.279076314236081</v>
       </c>
       <c r="C3" t="n">
-        <v>4.631028493950805</v>
+        <v>4.608271582166364</v>
       </c>
       <c r="D3" t="n">
-        <v>6.122743282547692</v>
+        <v>6.119287530628744</v>
       </c>
       <c r="E3" t="n">
-        <v>12.00276734107645</v>
+        <v>12.00663542703119</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.368612409099776</v>
+        <v>1.439778636860587</v>
       </c>
       <c r="C4" t="n">
-        <v>5.153493801182257</v>
+        <v>5.051683091576357</v>
       </c>
       <c r="D4" t="n">
-        <v>6.44379428272487</v>
+        <v>6.411671419804263</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9659004930069</v>
+        <v>12.90313314824121</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.527880509080755</v>
+        <v>1.656323895970053</v>
       </c>
       <c r="C5" t="n">
-        <v>5.813639590422822</v>
+        <v>5.58565163385025</v>
       </c>
       <c r="D5" t="n">
-        <v>6.730858913493433</v>
+        <v>6.789933020693697</v>
       </c>
       <c r="E5" t="n">
-        <v>14.07237901299701</v>
+        <v>14.031908550514</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.716864670738296</v>
+        <v>1.900559818302736</v>
       </c>
       <c r="C6" t="n">
-        <v>6.645327844722636</v>
+        <v>6.251219051024403</v>
       </c>
       <c r="D6" t="n">
-        <v>7.198216871941433</v>
+        <v>7.173463872612531</v>
       </c>
       <c r="E6" t="n">
-        <v>15.56040938740236</v>
+        <v>15.32524274193967</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.929796801212321</v>
+        <v>2.186131228329353</v>
       </c>
       <c r="C7" t="n">
-        <v>7.611469784362565</v>
+        <v>7.020140897064088</v>
       </c>
       <c r="D7" t="n">
-        <v>7.577981226522394</v>
+        <v>7.66587923532262</v>
       </c>
       <c r="E7" t="n">
-        <v>17.11924781209728</v>
+        <v>16.87215136071606</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.180580790572406</v>
+        <v>1.396954100077359</v>
       </c>
       <c r="C8" t="n">
-        <v>5.246692761423561</v>
+        <v>4.66442964094432</v>
       </c>
       <c r="D8" t="n">
-        <v>5.892066666650005</v>
+        <v>5.960341817200889</v>
       </c>
       <c r="E8" t="n">
-        <v>12.31934021864597</v>
+        <v>12.02172555822257</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.484778322347056</v>
+        <v>1.776155740635681</v>
       </c>
       <c r="C9" t="n">
-        <v>6.440721544802051</v>
+        <v>5.632364216521812</v>
       </c>
       <c r="D9" t="n">
-        <v>6.421410067878454</v>
+        <v>6.648659502657309</v>
       </c>
       <c r="E9" t="n">
-        <v>14.34690993502756</v>
+        <v>14.0571794598148</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.801333637978788</v>
+        <v>2.173034587111377</v>
       </c>
       <c r="C10" t="n">
-        <v>7.818236681341317</v>
+        <v>6.731679187785224</v>
       </c>
       <c r="D10" t="n">
-        <v>6.957755645923555</v>
+        <v>7.353903754485602</v>
       </c>
       <c r="E10" t="n">
-        <v>16.57732596524366</v>
+        <v>16.2586175293822</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.117085184011152</v>
+        <v>2.57696503203316</v>
       </c>
       <c r="C11" t="n">
-        <v>9.343910210334851</v>
+        <v>7.919917976104437</v>
       </c>
       <c r="D11" t="n">
-        <v>7.484113351064657</v>
+        <v>7.942296619691303</v>
       </c>
       <c r="E11" t="n">
-        <v>18.94510874541066</v>
+        <v>18.4391796278289</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.415491078922624</v>
+        <v>3.004767358733503</v>
       </c>
       <c r="C12" t="n">
-        <v>10.96834771889737</v>
+        <v>9.180058030434168</v>
       </c>
       <c r="D12" t="n">
-        <v>7.990119493940383</v>
+        <v>8.644419720819712</v>
       </c>
       <c r="E12" t="n">
-        <v>21.37395829176037</v>
+        <v>20.82924510998738</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.70003385891077</v>
+        <v>3.419051628612332</v>
       </c>
       <c r="C13" t="n">
-        <v>12.63097423345327</v>
+        <v>10.44631659213176</v>
       </c>
       <c r="D13" t="n">
-        <v>8.459984922830733</v>
+        <v>9.213260577859716</v>
       </c>
       <c r="E13" t="n">
-        <v>23.79099301519478</v>
+        <v>23.07862879860381</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.548206312120178</v>
+        <v>1.971496652283232</v>
       </c>
       <c r="C14" t="n">
-        <v>8.875558842582587</v>
+        <v>7.357452915074616</v>
       </c>
       <c r="D14" t="n">
-        <v>6.386504435574522</v>
+        <v>7.003405240492089</v>
       </c>
       <c r="E14" t="n">
-        <v>16.81026959027729</v>
+        <v>16.33235480784994</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.570177825741221</v>
+        <v>2.044970650469064</v>
       </c>
       <c r="C15" t="n">
-        <v>9.632535409942088</v>
+        <v>7.819188495335977</v>
       </c>
       <c r="D15" t="n">
-        <v>6.393828273448203</v>
+        <v>7.124660899443612</v>
       </c>
       <c r="E15" t="n">
-        <v>17.59654150913151</v>
+        <v>16.98882004524865</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.79920974766496</v>
+        <v>2.399519016380756</v>
       </c>
       <c r="C16" t="n">
-        <v>11.45785964654001</v>
+        <v>9.134229727697537</v>
       </c>
       <c r="D16" t="n">
-        <v>6.821025969474158</v>
+        <v>7.79024657301478</v>
       </c>
       <c r="E16" t="n">
-        <v>20.07809536367913</v>
+        <v>19.32399531709308</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.427961853304028</v>
+        <v>1.939216787767597</v>
       </c>
       <c r="C17" t="n">
-        <v>10.64044669050708</v>
+        <v>8.35906137537834</v>
       </c>
       <c r="D17" t="n">
-        <v>6.306766887035596</v>
+        <v>7.359760022179596</v>
       </c>
       <c r="E17" t="n">
-        <v>18.3751754308467</v>
+        <v>17.65803818532553</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.608750693041079</v>
+        <v>2.232032858036251</v>
       </c>
       <c r="C18" t="n">
-        <v>12.47896561625008</v>
+        <v>9.649951614215428</v>
       </c>
       <c r="D18" t="n">
-        <v>6.754002053705229</v>
+        <v>7.98435772909846</v>
       </c>
       <c r="E18" t="n">
-        <v>20.84171836299639</v>
+        <v>19.86634220135014</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.596115600087422</v>
+        <v>2.260287556964474</v>
       </c>
       <c r="C19" t="n">
-        <v>13.41707463504312</v>
+        <v>10.22961472871092</v>
       </c>
       <c r="D19" t="n">
-        <v>6.833317450731331</v>
+        <v>8.198172561606373</v>
       </c>
       <c r="E19" t="n">
-        <v>21.84650768586187</v>
+        <v>20.68807484728176</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.756415365236841</v>
+        <v>2.547841459538365</v>
       </c>
       <c r="C20" t="n">
-        <v>15.42266738509484</v>
+        <v>11.73406454565281</v>
       </c>
       <c r="D20" t="n">
-        <v>7.236040176490413</v>
+        <v>8.888213570490327</v>
       </c>
       <c r="E20" t="n">
-        <v>24.4151229268221</v>
+        <v>23.1701195756815</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.033004751885537</v>
+        <v>1.527461983129442</v>
       </c>
       <c r="C21" t="n">
-        <v>11.33369801438392</v>
+        <v>8.648117351939728</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016444455935729</v>
+        <v>7.509074030518494</v>
       </c>
       <c r="E21" t="n">
-        <v>18.38314722220519</v>
+        <v>17.68465336558766</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_27_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_27_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.279076314236081</v>
+        <v>1.259834059232843</v>
       </c>
       <c r="C3" t="n">
-        <v>4.608271582166364</v>
+        <v>4.635465993574001</v>
       </c>
       <c r="D3" t="n">
-        <v>6.119287530628744</v>
+        <v>6.0540405782045</v>
       </c>
       <c r="E3" t="n">
-        <v>12.00663542703119</v>
+        <v>11.94934063101134</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.439778636860587</v>
+        <v>1.391093787210565</v>
       </c>
       <c r="C4" t="n">
-        <v>5.051683091576357</v>
+        <v>5.136400510459728</v>
       </c>
       <c r="D4" t="n">
-        <v>6.411671419804263</v>
+        <v>6.30667466006808</v>
       </c>
       <c r="E4" t="n">
-        <v>12.90313314824121</v>
+        <v>12.83416895773837</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.656323895970053</v>
+        <v>1.569061103265209</v>
       </c>
       <c r="C5" t="n">
-        <v>5.58565163385025</v>
+        <v>5.791964571432404</v>
       </c>
       <c r="D5" t="n">
-        <v>6.789933020693697</v>
+        <v>6.693638524316704</v>
       </c>
       <c r="E5" t="n">
-        <v>14.031908550514</v>
+        <v>14.05466419901432</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.900559818302736</v>
+        <v>1.771923583143978</v>
       </c>
       <c r="C6" t="n">
-        <v>6.251219051024403</v>
+        <v>6.591341087527112</v>
       </c>
       <c r="D6" t="n">
-        <v>7.173463872612531</v>
+        <v>6.987122105862164</v>
       </c>
       <c r="E6" t="n">
-        <v>15.32524274193967</v>
+        <v>15.35038677653325</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.186131228329353</v>
+        <v>2.000579568406673</v>
       </c>
       <c r="C7" t="n">
-        <v>7.020140897064088</v>
+        <v>7.529865823259052</v>
       </c>
       <c r="D7" t="n">
-        <v>7.66587923532262</v>
+        <v>7.325278953355318</v>
       </c>
       <c r="E7" t="n">
-        <v>16.87215136071606</v>
+        <v>16.85572434502104</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.396954100077359</v>
+        <v>1.221249232072371</v>
       </c>
       <c r="C8" t="n">
-        <v>4.66442964094432</v>
+        <v>5.185099147023147</v>
       </c>
       <c r="D8" t="n">
-        <v>5.960341817200889</v>
+        <v>5.540516640664684</v>
       </c>
       <c r="E8" t="n">
-        <v>12.02172555822257</v>
+        <v>11.9468650197602</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.776155740635681</v>
+        <v>1.522045722528784</v>
       </c>
       <c r="C9" t="n">
-        <v>5.632364216521812</v>
+        <v>6.389559205793988</v>
       </c>
       <c r="D9" t="n">
-        <v>6.648659502657309</v>
+        <v>5.983234171146147</v>
       </c>
       <c r="E9" t="n">
-        <v>14.0571794598148</v>
+        <v>13.89483909946892</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.173034587111377</v>
+        <v>1.832496065880692</v>
       </c>
       <c r="C10" t="n">
-        <v>6.731679187785224</v>
+        <v>7.757928671198065</v>
       </c>
       <c r="D10" t="n">
-        <v>7.353903754485602</v>
+        <v>6.428127612288348</v>
       </c>
       <c r="E10" t="n">
-        <v>16.2586175293822</v>
+        <v>16.01855234936711</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.57696503203316</v>
+        <v>2.145733320394756</v>
       </c>
       <c r="C11" t="n">
-        <v>7.919917976104437</v>
+        <v>9.223371100391148</v>
       </c>
       <c r="D11" t="n">
-        <v>7.942296619691303</v>
+        <v>6.921523567519706</v>
       </c>
       <c r="E11" t="n">
-        <v>18.4391796278289</v>
+        <v>18.29062798830561</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.004767358733503</v>
+        <v>2.467902245278859</v>
       </c>
       <c r="C12" t="n">
-        <v>9.180058030434168</v>
+        <v>10.7518936373735</v>
       </c>
       <c r="D12" t="n">
-        <v>8.644419720819712</v>
+        <v>7.455484260118506</v>
       </c>
       <c r="E12" t="n">
-        <v>20.82924510998738</v>
+        <v>20.67528014277087</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.419051628612332</v>
+        <v>2.798406773056255</v>
       </c>
       <c r="C13" t="n">
-        <v>10.44631659213176</v>
+        <v>12.36520244900201</v>
       </c>
       <c r="D13" t="n">
-        <v>9.213260577859716</v>
+        <v>7.960191681169927</v>
       </c>
       <c r="E13" t="n">
-        <v>23.07862879860381</v>
+        <v>23.1238009032282</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.971496652283232</v>
+        <v>1.630447317304933</v>
       </c>
       <c r="C14" t="n">
-        <v>7.357452915074616</v>
+        <v>8.681496773884119</v>
       </c>
       <c r="D14" t="n">
-        <v>7.003405240492089</v>
+        <v>6.052307699571864</v>
       </c>
       <c r="E14" t="n">
-        <v>16.33235480784994</v>
+        <v>16.36425179076092</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.044970650469064</v>
+        <v>1.674822313536889</v>
       </c>
       <c r="C15" t="n">
-        <v>7.819188495335977</v>
+        <v>9.375445138630978</v>
       </c>
       <c r="D15" t="n">
-        <v>7.124660899443612</v>
+        <v>6.077244091259733</v>
       </c>
       <c r="E15" t="n">
-        <v>16.98882004524865</v>
+        <v>17.1275115434276</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.399519016380756</v>
+        <v>1.953933185854257</v>
       </c>
       <c r="C16" t="n">
-        <v>9.134229727697537</v>
+        <v>11.0861994181433</v>
       </c>
       <c r="D16" t="n">
-        <v>7.79024657301478</v>
+        <v>6.568304475446944</v>
       </c>
       <c r="E16" t="n">
-        <v>19.32399531709308</v>
+        <v>19.6084370794445</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.939216787767597</v>
+        <v>1.57068833454743</v>
       </c>
       <c r="C17" t="n">
-        <v>8.35906137537834</v>
+        <v>10.227091637111</v>
       </c>
       <c r="D17" t="n">
-        <v>7.359760022179596</v>
+        <v>6.101159465335185</v>
       </c>
       <c r="E17" t="n">
-        <v>17.65803818532553</v>
+        <v>17.89893943699362</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.232032858036251</v>
+        <v>1.798326174731137</v>
       </c>
       <c r="C18" t="n">
-        <v>9.649951614215428</v>
+        <v>11.94295100468541</v>
       </c>
       <c r="D18" t="n">
-        <v>7.98435772909846</v>
+        <v>6.51382729533829</v>
       </c>
       <c r="E18" t="n">
-        <v>19.86634220135014</v>
+        <v>20.25510447475483</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.260287556964474</v>
+        <v>1.805787457283413</v>
       </c>
       <c r="C19" t="n">
-        <v>10.22961472871092</v>
+        <v>12.77885026998931</v>
       </c>
       <c r="D19" t="n">
-        <v>8.198172561606373</v>
+        <v>6.64282894367632</v>
       </c>
       <c r="E19" t="n">
-        <v>20.68807484728176</v>
+        <v>21.22746667094904</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.547841459538365</v>
+        <v>2.017599524474663</v>
       </c>
       <c r="C20" t="n">
-        <v>11.73406454565281</v>
+        <v>14.71780198587676</v>
       </c>
       <c r="D20" t="n">
-        <v>8.888213570490327</v>
+        <v>7.090496079335823</v>
       </c>
       <c r="E20" t="n">
-        <v>23.1701195756815</v>
+        <v>23.82589758968724</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.527461983129442</v>
+        <v>1.207785295672596</v>
       </c>
       <c r="C21" t="n">
-        <v>8.648117351939728</v>
+        <v>10.85830632355649</v>
       </c>
       <c r="D21" t="n">
-        <v>7.509074030518494</v>
+        <v>5.929716863742566</v>
       </c>
       <c r="E21" t="n">
-        <v>17.68465336558766</v>
+        <v>17.99580848297165</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_27_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_27_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.259834059232843</v>
+        <v>2.576272394936882</v>
       </c>
       <c r="C3" t="n">
-        <v>4.635465993574001</v>
+        <v>7.796634919925932</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0540405782045</v>
+        <v>8.208567074851768</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94934063101134</v>
+        <v>18.58147438971458</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.391093787210565</v>
+        <v>1.045837036816211</v>
       </c>
       <c r="C4" t="n">
-        <v>5.136400510459728</v>
+        <v>4.681790919952043</v>
       </c>
       <c r="D4" t="n">
-        <v>6.30667466006808</v>
+        <v>5.768562379754393</v>
       </c>
       <c r="E4" t="n">
-        <v>12.83416895773837</v>
+        <v>11.49619033652265</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.569061103265209</v>
+        <v>1.118631974057774</v>
       </c>
       <c r="C5" t="n">
-        <v>5.791964571432404</v>
+        <v>5.527557999097024</v>
       </c>
       <c r="D5" t="n">
-        <v>6.693638524316704</v>
+        <v>6.074483552115773</v>
       </c>
       <c r="E5" t="n">
-        <v>14.05466419901432</v>
+        <v>12.72067352527057</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.771923583143978</v>
+        <v>1.19504772681854</v>
       </c>
       <c r="C6" t="n">
-        <v>6.591341087527112</v>
+        <v>6.57874894042083</v>
       </c>
       <c r="D6" t="n">
-        <v>6.987122105862164</v>
+        <v>6.434715712228911</v>
       </c>
       <c r="E6" t="n">
-        <v>15.35038677653325</v>
+        <v>14.20851237946828</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.000579568406673</v>
+        <v>1.266277334492287</v>
       </c>
       <c r="C7" t="n">
-        <v>7.529865823259052</v>
+        <v>7.8217777607992</v>
       </c>
       <c r="D7" t="n">
-        <v>7.325278953355318</v>
+        <v>6.840826167509424</v>
       </c>
       <c r="E7" t="n">
-        <v>16.85572434502104</v>
+        <v>15.92888126280091</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.221249232072371</v>
+        <v>1.337532156045239</v>
       </c>
       <c r="C8" t="n">
-        <v>5.185099147023147</v>
+        <v>9.238461724887582</v>
       </c>
       <c r="D8" t="n">
-        <v>5.540516640664684</v>
+        <v>7.203919616921564</v>
       </c>
       <c r="E8" t="n">
-        <v>11.9468650197602</v>
+        <v>17.77991349785438</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.522045722528784</v>
+        <v>1.395131220264788</v>
       </c>
       <c r="C9" t="n">
-        <v>6.389559205793988</v>
+        <v>10.86211775411619</v>
       </c>
       <c r="D9" t="n">
-        <v>5.983234171146147</v>
+        <v>7.564983283584876</v>
       </c>
       <c r="E9" t="n">
-        <v>13.89483909946892</v>
+        <v>19.82223225796585</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.832496065880692</v>
+        <v>0.8959135024645116</v>
       </c>
       <c r="C10" t="n">
-        <v>7.757928671198065</v>
+        <v>7.906024079776606</v>
       </c>
       <c r="D10" t="n">
-        <v>6.428127612288348</v>
+        <v>5.947074163153649</v>
       </c>
       <c r="E10" t="n">
-        <v>16.01855234936711</v>
+        <v>14.74901174539477</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.145733320394756</v>
+        <v>0.7985143127261857</v>
       </c>
       <c r="C11" t="n">
-        <v>9.223371100391148</v>
+        <v>8.690744837258125</v>
       </c>
       <c r="D11" t="n">
-        <v>6.921523567519706</v>
+        <v>5.776407142247383</v>
       </c>
       <c r="E11" t="n">
-        <v>18.29062798830561</v>
+        <v>15.26566629223169</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.467902245278859</v>
+        <v>0.8240103006054754</v>
       </c>
       <c r="C12" t="n">
-        <v>10.7518936373735</v>
+        <v>10.45770417283858</v>
       </c>
       <c r="D12" t="n">
-        <v>7.455484260118506</v>
+        <v>6.117309215070045</v>
       </c>
       <c r="E12" t="n">
-        <v>20.67528014277087</v>
+        <v>17.3990236885141</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.798406773056255</v>
+        <v>0.6325302283691775</v>
       </c>
       <c r="C13" t="n">
-        <v>12.36520244900201</v>
+        <v>10.04053012087298</v>
       </c>
       <c r="D13" t="n">
-        <v>7.960191681169927</v>
+        <v>5.544498699550202</v>
       </c>
       <c r="E13" t="n">
-        <v>23.1238009032282</v>
+        <v>16.21755904879236</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.630447317304933</v>
+        <v>0.6568677539574558</v>
       </c>
       <c r="C14" t="n">
-        <v>8.681496773884119</v>
+        <v>11.8667084779736</v>
       </c>
       <c r="D14" t="n">
-        <v>6.052307699571864</v>
+        <v>5.843077628842784</v>
       </c>
       <c r="E14" t="n">
-        <v>16.36425179076092</v>
+        <v>18.36665386077384</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.674822313536889</v>
+        <v>0.6154772707464103</v>
       </c>
       <c r="C15" t="n">
-        <v>9.375445138630978</v>
+        <v>12.88253264503482</v>
       </c>
       <c r="D15" t="n">
-        <v>6.077244091259733</v>
+        <v>5.845610537919741</v>
       </c>
       <c r="E15" t="n">
-        <v>17.1275115434276</v>
+        <v>19.34362045370097</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.953933185854257</v>
+        <v>0.6572408180850696</v>
       </c>
       <c r="C16" t="n">
-        <v>11.0861994181433</v>
+        <v>14.94226878097575</v>
       </c>
       <c r="D16" t="n">
-        <v>6.568304475446944</v>
+        <v>6.199579672685928</v>
       </c>
       <c r="E16" t="n">
-        <v>19.6084370794445</v>
+        <v>21.79908927174675</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.57068833454743</v>
+        <v>0.3944269576581986</v>
       </c>
       <c r="C17" t="n">
-        <v>10.227091637111</v>
+        <v>11.02362281947461</v>
       </c>
       <c r="D17" t="n">
-        <v>6.101159465335185</v>
+        <v>5.121581423514761</v>
       </c>
       <c r="E17" t="n">
-        <v>17.89893943699362</v>
+        <v>16.53963120064757</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.798326174731137</v>
+        <v>0.2969001407183204</v>
       </c>
       <c r="C18" t="n">
-        <v>11.94295100468541</v>
+        <v>9.839330746364638</v>
       </c>
       <c r="D18" t="n">
-        <v>6.51382729533829</v>
+        <v>4.613193192347593</v>
       </c>
       <c r="E18" t="n">
-        <v>20.25510447475483</v>
+        <v>14.74942407943055</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.805787457283413</v>
+        <v>0.3418740030498668</v>
       </c>
       <c r="C19" t="n">
-        <v>12.77885026998931</v>
+        <v>12.02261001340799</v>
       </c>
       <c r="D19" t="n">
-        <v>6.64282894367632</v>
+        <v>5.032311104767598</v>
       </c>
       <c r="E19" t="n">
-        <v>21.22746667094904</v>
+        <v>17.39679512122546</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.017599524474663</v>
+        <v>0.3837357251589508</v>
       </c>
       <c r="C20" t="n">
-        <v>14.71780198587676</v>
+        <v>14.29233216581028</v>
       </c>
       <c r="D20" t="n">
-        <v>7.090496079335823</v>
+        <v>5.44122865854048</v>
       </c>
       <c r="E20" t="n">
-        <v>23.82589758968724</v>
+        <v>20.11729654950971</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.207785295672596</v>
+        <v>0.4201880174176348</v>
       </c>
       <c r="C21" t="n">
-        <v>10.85830632355649</v>
+        <v>16.63156205567324</v>
       </c>
       <c r="D21" t="n">
-        <v>5.929716863742566</v>
+        <v>5.820821408387508</v>
       </c>
       <c r="E21" t="n">
-        <v>17.99580848297165</v>
+        <v>22.87257148147838</v>
       </c>
     </row>
   </sheetData>
